--- a/outputs/SA_negative_prices.xlsx
+++ b/outputs/SA_negative_prices.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3372,6 +3372,40 @@
         <v>1.46</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3383,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6306,8 +6340,42 @@
         <v>1.46</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B85">
+  <conditionalFormatting sqref="B2:B86">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6319,7 +6387,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C85">
+  <conditionalFormatting sqref="C2:C86">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6331,7 +6399,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D85">
+  <conditionalFormatting sqref="D2:D86">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6343,7 +6411,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E85">
+  <conditionalFormatting sqref="E2:E86">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6355,7 +6423,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F85">
+  <conditionalFormatting sqref="F2:F86">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6367,7 +6435,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G85">
+  <conditionalFormatting sqref="G2:G86">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6379,7 +6447,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H85">
+  <conditionalFormatting sqref="H2:H86">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6391,7 +6459,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I85">
+  <conditionalFormatting sqref="I2:I86">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6403,7 +6471,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J85">
+  <conditionalFormatting sqref="J2:J86">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6425,7 +6493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9606,6 +9674,43 @@
         <v>42</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>2976</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>551</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/SA_negative_prices.xlsx
+++ b/outputs/SA_negative_prices.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3406,6 +3406,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3417,7 +3451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6374,8 +6408,42 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B86">
+  <conditionalFormatting sqref="B2:B87">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6387,7 +6455,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C86">
+  <conditionalFormatting sqref="C2:C87">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6399,7 +6467,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D86">
+  <conditionalFormatting sqref="D2:D87">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6411,7 +6479,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E86">
+  <conditionalFormatting sqref="E2:E87">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6423,7 +6491,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F86">
+  <conditionalFormatting sqref="F2:F87">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6435,7 +6503,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G86">
+  <conditionalFormatting sqref="G2:G87">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6447,7 +6515,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H86">
+  <conditionalFormatting sqref="H2:H87">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6459,7 +6527,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I86">
+  <conditionalFormatting sqref="I2:I87">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6471,7 +6539,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J86">
+  <conditionalFormatting sqref="J2:J87">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6493,7 +6561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9711,6 +9779,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>2880</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>620</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/SA_negative_prices.xlsx
+++ b/outputs/SA_negative_prices.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Percentages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Audit" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Percentages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1.08</v>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5.58</v>
+        <v>5.48</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>3.9</v>
@@ -625,31 +625,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>14.08</v>
+        <v>13.84</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>11.39</v>
+        <v>11.36</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.36</v>
+        <v>11.32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>11.26</v>
+        <v>11.22</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>9.34</v>
+        <v>9.31</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6.35</v>
+        <v>6.32</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>5.88</v>
+        <v>5.85</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="6">
@@ -659,31 +659,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>15</v>
+        <v>14.69</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.64</v>
+        <v>12.5</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>12.57</v>
+        <v>12.43</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>12.36</v>
+        <v>12.22</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>11.01</v>
+        <v>10.87</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>6.94</v>
+        <v>6.88</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6.84</v>
+        <v>6.77</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="7">
@@ -693,31 +693,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>11.49</v>
+        <v>11.46</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.99</v>
+        <v>10.95</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>10.82</v>
+        <v>10.79</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>10.11</v>
+        <v>10.08</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>9.34</v>
+        <v>9.24</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8.84</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="8">
@@ -727,22 +727,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14.69</v>
+        <v>14.76</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12.47</v>
+        <v>12.57</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.33</v>
+        <v>12.43</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>12.26</v>
+        <v>12.36</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>11.81</v>
+        <v>11.91</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>11.42</v>
+        <v>11.53</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>8.609999999999999</v>
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5.28</v>
+        <v>5.07</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6.59</v>
+        <v>6.62</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>1.61</v>
@@ -829,31 +829,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>13.47</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>12.9</v>
+        <v>12.97</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>12.86</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>12.79</v>
-      </c>
       <c r="F11" s="3" t="n">
-        <v>7.11</v>
+        <v>7.15</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>6.36</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>6.32</v>
-      </c>
       <c r="I11" s="3" t="n">
-        <v>6.11</v>
+        <v>6.14</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="12">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5.24</v>
+        <v>3.7</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>2.65</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>7.5</v>
+        <v>6.74</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>3.4</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5.68</v>
+        <v>5.01</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1.98</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.9</v>
@@ -999,31 +999,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.96</v>
+        <v>2.55</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G16" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I16" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="J16" s="3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17">
@@ -1067,31 +1067,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>32.15</v>
+        <v>32.12</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>27.12</v>
+        <v>27.26</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>26.81</v>
+        <v>26.94</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>25.49</v>
+        <v>25.62</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>12.99</v>
+        <v>13.09</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11.7</v>
+        <v>11.81</v>
       </c>
       <c r="H18" s="3" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>10.28</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <v>10.24</v>
-      </c>
       <c r="J18" s="3" t="n">
-        <v>9.58</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1101,31 +1101,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>22.65</v>
+        <v>22.24</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>19.05</v>
+        <v>18.95</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>18.21</v>
+        <v>18.11</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>17.67</v>
+        <v>17.64</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>10.72</v>
+        <v>10.75</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>8.57</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>8.529999999999999</v>
-      </c>
       <c r="J19" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="20">
@@ -1135,28 +1135,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>19.38</v>
+        <v>19.24</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>15.94</v>
+        <v>15.9</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>15.56</v>
+        <v>15.52</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>15.24</v>
+        <v>15.21</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>8.539999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>7.22</v>
+        <v>7.19</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>4.65</v>
@@ -1169,31 +1169,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>33.97</v>
+        <v>33.43</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>28.12</v>
+        <v>28.26</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>27.02</v>
+        <v>27.15</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>26.11</v>
+        <v>26.24</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>16.16</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>12.97</v>
+        <v>13</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10.72</v>
+        <v>10.75</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>10.55</v>
+        <v>10.58</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="22">
@@ -1203,22 +1203,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>32.69</v>
+        <v>32.49</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>27.18</v>
+        <v>27.32</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>25.03</v>
+        <v>25.17</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>22.08</v>
+        <v>22.21</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>11.63</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>8.029999999999999</v>
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>33.97</v>
+        <v>34.23</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>29.72</v>
+        <v>30.02</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.05</v>
+        <v>28.35</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>27.08</v>
+        <v>27.42</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>14.77</v>
+        <v>14.73</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>11.31</v>
@@ -1271,31 +1271,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>21.1</v>
+        <v>21.07</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>18.78</v>
+        <v>18.82</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>17.88</v>
+        <v>17.91</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>16.47</v>
+        <v>16.5</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>9.51</v>
+        <v>9.58</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>17.6</v>
+        <v>17.26</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>12.5</v>
@@ -1317,10 +1317,10 @@
         <v>8.09</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4.55</v>
+        <v>4.51</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>2.22</v>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>8.699999999999999</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>15.36</v>
+        <v>15.29</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>12.67</v>
@@ -1422,7 +1422,7 @@
         <v>4.4</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>2.62</v>
@@ -1441,16 +1441,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>38.81</v>
+        <v>38.94</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>33</v>
+        <v>33.06</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>29.67</v>
+        <v>29.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>22.65</v>
+        <v>22.68</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>9.140000000000001</v>
@@ -1475,22 +1475,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>62.74</v>
+        <v>62.64</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>56.6</v>
+        <v>56.53</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>50.69</v>
+        <v>50.66</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>42.15</v>
+        <v>42.12</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>16.35</v>
+        <v>16.32</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>14.41</v>
+        <v>14.37</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>12.29</v>
@@ -1509,31 +1509,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>80.84999999999999</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>74.45999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>69.93000000000001</v>
+        <v>70.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>64.48</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>46.37</v>
+        <v>46.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>26.78</v>
+        <v>26.71</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.82</v>
+        <v>18.75</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>17.88</v>
+        <v>17.81</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>15.29</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="32">
@@ -1543,31 +1543,31 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>42.01</v>
+        <v>41.88</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>38.51</v>
+        <v>38.58</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>36.6</v>
+        <v>36.63</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>34.51</v>
+        <v>34.62</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>22.92</v>
+        <v>22.95</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>12.81</v>
+        <v>12.74</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>9.1</v>
+        <v>8.99</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="33">
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>50.5</v>
+        <v>50.37</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>42.14</v>
+        <v>42</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>38.98</v>
+        <v>39.01</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>34.17</v>
+        <v>34.24</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>24.29</v>
+        <v>24.5</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>4.87</v>
+        <v>4.84</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>3.43</v>
+        <v>3.39</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1617,22 +1617,22 @@
         <v>28.8</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>26.61</v>
+        <v>26.75</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>25.34</v>
+        <v>25.44</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>16.53</v>
+        <v>16.63</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>5.51</v>
+        <v>5.54</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>2.12</v>
@@ -1645,28 +1645,28 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>41.44</v>
+        <v>41.37</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>37.87</v>
+        <v>37.91</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>34.75</v>
+        <v>34.78</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>32.4</v>
+        <v>32.44</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>21.54</v>
+        <v>21.65</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>5.95</v>
+        <v>6.03</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4.87</v>
+        <v>4.95</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>3.2</v>
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>36.59</v>
+        <v>36.49</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>26.58</v>
+        <v>26.61</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>23.62</v>
+        <v>23.72</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>18.82</v>
+        <v>18.92</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8.06</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>25.03</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>23.09</v>
+        <v>23.12</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>22.01</v>
+        <v>22.05</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>20.97</v>
+        <v>21.01</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>17.78</v>
+        <v>17.85</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>8.06</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>6.63</v>
+        <v>6.7</v>
       </c>
       <c r="I37" s="3" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J37" s="3" t="n">
         <v>6.49</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>6.46</v>
       </c>
     </row>
     <row r="38">
@@ -1747,16 +1747,16 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>21.81</v>
+        <v>21.88</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>21.47</v>
+        <v>21.54</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>21.14</v>
+        <v>21.2</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>20.9</v>
+        <v>20.97</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>16.97</v>
@@ -1781,31 +1781,31 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>14.44</v>
+        <v>14.55</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>14.03</v>
+        <v>14.13</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>13.51</v>
+        <v>13.61</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.23</v>
+        <v>13.33</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>10.1</v>
+        <v>10.17</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="40">
@@ -1815,22 +1815,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>22.98</v>
+        <v>22.92</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>22.72</v>
+        <v>22.68</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>21.34</v>
+        <v>21.3</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>21.07</v>
+        <v>21.03</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>15.52</v>
+        <v>15.46</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10.65</v>
+        <v>10.58</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>5.44</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>34.31</v>
+        <v>34.48</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>32.83</v>
+        <v>33.03</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>31.12</v>
+        <v>31.28</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>29.4</v>
+        <v>29.64</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>22.88</v>
+        <v>23.08</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>13.58</v>
+        <v>13.68</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>8.94</v>
@@ -1883,31 +1883,31 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>45.03</v>
+        <v>45</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>43.47</v>
+        <v>43.54</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>40.59</v>
+        <v>40.66</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>38.06</v>
+        <v>38.16</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>28.92</v>
+        <v>28.99</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>23.12</v>
+        <v>23.19</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>15.94</v>
+        <v>15.97</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>13.51</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>6.77</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="43">
@@ -1917,28 +1917,28 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>52.86</v>
+        <v>52.96</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>50.94</v>
+        <v>51.04</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>48.69</v>
+        <v>48.79</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46.03</v>
+        <v>46.14</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>38.58</v>
+        <v>38.64</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>33.43</v>
+        <v>33.53</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>28.43</v>
+        <v>28.53</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>18.75</v>
+        <v>18.78</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>12.06</v>
@@ -1951,31 +1951,31 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>61.88</v>
+        <v>61.84</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>58.02</v>
+        <v>58.06</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>56.15</v>
+        <v>56.22</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>53.61</v>
+        <v>53.72</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>43.61</v>
+        <v>43.68</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>39.65</v>
+        <v>39.72</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>34.13</v>
+        <v>34.2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>18.33</v>
+        <v>18.26</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.21</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="45">
@@ -1985,31 +1985,31 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>82.53</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>79.06999999999999</v>
+        <v>78.83</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>75.47</v>
+        <v>75.27</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>72.01000000000001</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>63.78</v>
+        <v>63.81</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>55.31</v>
+        <v>55.54</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>38.98</v>
+        <v>39.15</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>20.43</v>
+        <v>20.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>9.74</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2019,31 +2019,31 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>58.64</v>
+        <v>58.7</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>56.45</v>
+        <v>56.55</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>54.57</v>
+        <v>54.64</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>52.92</v>
+        <v>52.99</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>45.67</v>
+        <v>45.7</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>36.42</v>
+        <v>36.49</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>11.59</v>
+        <v>11.63</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.96</v>
+        <v>6.99</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.81</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="47">
@@ -2053,31 +2053,31 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>63.73</v>
+        <v>63.84</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>60.31</v>
+        <v>60.38</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>57.37</v>
+        <v>57.44</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>55.62</v>
+        <v>55.73</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>40.77</v>
+        <v>41.07</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>24.44</v>
+        <v>24.59</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>7.7</v>
+        <v>7.74</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>6.73</v>
+        <v>6.77</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="48">
@@ -2090,16 +2090,16 @@
         <v>57.22</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>53.36</v>
+        <v>53.46</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>48.86</v>
+        <v>49.03</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46.47</v>
+        <v>46.67</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>38.17</v>
+        <v>38.37</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>17.71</v>
@@ -2124,28 +2124,28 @@
         <v>42.05</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>39.62</v>
+        <v>39.72</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>36.74</v>
+        <v>36.84</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>34.17</v>
+        <v>34.31</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>29.13</v>
+        <v>29.2</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>13.33</v>
+        <v>13.37</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>8.51</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>8.02</v>
+        <v>8.06</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>7.92</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="50">
@@ -2158,19 +2158,19 @@
         <v>15.42</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>14.65</v>
+        <v>14.72</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.68</v>
+        <v>13.74</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>12.57</v>
+        <v>12.63</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>11.32</v>
+        <v>11.39</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>6.28</v>
+        <v>6.35</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>2.59</v>
@@ -2192,16 +2192,16 @@
         <v>29.69</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>27.85</v>
+        <v>27.88</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>25.83</v>
+        <v>25.9</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>24.41</v>
+        <v>24.44</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>22.19</v>
+        <v>22.22</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>15.03</v>
@@ -2223,22 +2223,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>35.69</v>
+        <v>35.38</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>27.59</v>
+        <v>27.69</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>24.87</v>
+        <v>24.93</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>21.07</v>
+        <v>21.14</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>14.62</v>
+        <v>14.65</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>5.88</v>
@@ -2257,22 +2257,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>39.92</v>
+        <v>39.89</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>35.82</v>
+        <v>35.95</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>33.47</v>
+        <v>33.6</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>31.55</v>
+        <v>31.69</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>29</v>
+        <v>29.13</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>20.46</v>
+        <v>20.5</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>9.880000000000001</v>
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>69.83</v>
+        <v>70</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>64.06</v>
+        <v>64.17</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>62.64</v>
+        <v>62.78</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>60.8</v>
+        <v>60.94</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>45.73</v>
+        <v>45.62</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>16.53</v>
@@ -2315,7 +2315,7 @@
         <v>11.18</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>10.35</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="55">
@@ -2325,25 +2325,25 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>72.38</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>70.03</v>
+        <v>70.16</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>64.34999999999999</v>
+        <v>64.45</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>62.57</v>
+        <v>62.63</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>60.01</v>
+        <v>60.11</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>17.24</v>
+        <v>17.27</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>13.24</v>
@@ -2359,31 +2359,31 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>68.58</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>66.53</v>
+        <v>66.63</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62.6</v>
+        <v>62.74</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>60.62</v>
+        <v>60.8</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>56.28</v>
+        <v>56.39</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>33.26</v>
+        <v>33.33</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>14.93</v>
+        <v>14.97</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>13.09</v>
+        <v>13.12</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>11.42</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="57">
@@ -2393,31 +2393,31 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>67.73999999999999</v>
+        <v>67.88</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>66.3</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>64.38</v>
+        <v>64.55</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>61.73</v>
+        <v>61.96</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>56.96</v>
+        <v>57.19</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>37.9</v>
+        <v>38.04</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>19.89</v>
+        <v>20.03</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>17</v>
+        <v>17.14</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>14.31</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="58">
@@ -2427,31 +2427,31 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>64.55</v>
+        <v>64.72</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>63.04</v>
+        <v>63.21</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>57.76</v>
+        <v>57.93</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>49.73</v>
+        <v>49.93</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>45.13</v>
+        <v>45.3</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>29.84</v>
+        <v>29.91</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>16.63</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>14.21</v>
+        <v>14.25</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>12.77</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="59">
@@ -2461,31 +2461,31 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>72.88</v>
+        <v>72.84</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>71.98</v>
+        <v>72.02</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>66.84999999999999</v>
+        <v>66.95</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>63.15</v>
+        <v>63.29</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>59.27</v>
+        <v>59.45</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>31.07</v>
+        <v>31.18</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>14.04</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>9.59</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>8.84</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2501,13 +2501,13 @@
         <v>46.94</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>42.2</v>
+        <v>42.17</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>38.61</v>
+        <v>38.64</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>31.92</v>
+        <v>31.99</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>12.63</v>
@@ -2532,16 +2532,16 @@
         <v>34.13</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>24.93</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>21.28</v>
+        <v>21.32</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>17.36</v>
+        <v>17.4</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>4.13</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>19.22</v>
+        <v>19.35</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>18.35</v>
+        <v>18.48</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>15.83</v>
+        <v>15.89</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>14.11</v>
+        <v>14.21</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>11.93</v>
+        <v>12.03</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>2.28</v>
@@ -2597,16 +2597,16 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>10.87</v>
+        <v>10.9</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>5.73</v>
+        <v>5.76</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>4.97</v>
@@ -2631,28 +2631,28 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>27.45</v>
+        <v>27.69</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>26.98</v>
+        <v>27.18</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>26.04</v>
+        <v>26.24</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>24.33</v>
+        <v>24.53</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>22.21</v>
+        <v>22.41</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>6.15</v>
+        <v>6.18</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>5.01</v>
@@ -2665,31 +2665,31 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>55.38</v>
+        <v>55.58</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>53.56</v>
+        <v>53.76</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>52.02</v>
+        <v>52.25</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>48.99</v>
+        <v>49.23</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>42.54</v>
+        <v>42.74</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>12.4</v>
+        <v>12.43</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>6.08</v>
+        <v>6.12</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>4.27</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="66">
@@ -2699,31 +2699,31 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>80.8</v>
+        <v>80.87</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>74.62</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>72.47</v>
+        <v>72.64</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>68.58</v>
+        <v>68.78</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>56.22</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>19.34</v>
+        <v>19.41</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>6.32</v>
+        <v>6.39</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>5.8</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="67">
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>92.84</v>
+        <v>92.81</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.87</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>90.73</v>
+        <v>90.86</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>87.67</v>
+        <v>87.77</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>75.91</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>36.86</v>
+        <v>36.96</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>22.55</v>
@@ -2767,31 +2767,31 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>65</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>64.03</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>61.7</v>
+        <v>61.94</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>53.33</v>
+        <v>53.54</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>34.27</v>
+        <v>34.31</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>23.54</v>
+        <v>23.58</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>15.94</v>
+        <v>16.01</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>10.66</v>
+        <v>10.73</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>10.03</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="69">
@@ -2801,31 +2801,31 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>75.91</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>74.45999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>70.73</v>
+        <v>70.77</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>60.58</v>
+        <v>60.62</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>33.57</v>
+        <v>33.4</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>25.47</v>
+        <v>25.37</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>15.89</v>
+        <v>15.73</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>9.44</v>
+        <v>9.41</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="70">
@@ -2835,31 +2835,31 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70.53</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>70.16</v>
+        <v>70.09</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>64.84999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>57.02</v>
+        <v>57.16</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>31.92</v>
+        <v>32.09</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>23.69</v>
+        <v>23.82</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>19.49</v>
+        <v>19.59</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>14.92</v>
+        <v>15.02</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>13.51</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="71">
@@ -2869,19 +2869,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>71.84</v>
+        <v>71.95</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>70.8</v>
+        <v>70.91</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>67.89</v>
+        <v>67.97</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>53.94</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>28.35</v>
+        <v>28.39</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>21.73</v>
@@ -2893,7 +2893,7 @@
         <v>16.96</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>15.74</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="72">
@@ -2906,28 +2906,28 @@
         <v>56.72</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>51.85</v>
+        <v>52.02</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>47.95</v>
+        <v>48.08</v>
       </c>
       <c r="E72" s="3" t="n">
         <v>26.41</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>15.15</v>
+        <v>15.12</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>11.9</v>
+        <v>11.86</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>11.29</v>
+        <v>11.26</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>10.79</v>
+        <v>10.75</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>9.07</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -2940,28 +2940,28 @@
         <v>43.3</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>38.54</v>
+        <v>38.65</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>31.81</v>
+        <v>31.94</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>6.91</v>
+        <v>6.94</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="74">
@@ -2971,31 +2971,31 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>32.9</v>
+        <v>32.93</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>31.05</v>
+        <v>31.25</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>21.61</v>
+        <v>21.71</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>6.85</v>
+        <v>6.92</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>4.91</v>
+        <v>4.97</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="I74" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J74" s="3" t="n">
         <v>3.26</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>3.19</v>
       </c>
     </row>
     <row r="75">
@@ -3005,19 +3005,19 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>21.39</v>
+        <v>21.46</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>19.27</v>
+        <v>19.34</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>12.36</v>
+        <v>12.47</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>5.24</v>
+        <v>5.31</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>3.37</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>35.92</v>
+        <v>36.12</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>33.3</v>
+        <v>33.53</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>14.92</v>
+        <v>13.47</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>4.97</v>
@@ -3073,22 +3073,22 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>42.71</v>
+        <v>42.78</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>35.45</v>
+        <v>35.62</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>9.58</v>
+        <v>8.94</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>2.92</v>
@@ -3107,22 +3107,22 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>73.58</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>58.89</v>
+        <v>59.13</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>17.57</v>
+        <v>17.53</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>10.03</v>
+        <v>10.1</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>8.23</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>3.96</v>
@@ -3141,31 +3141,31 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>78.83</v>
+        <v>79.03</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>32.83</v>
+        <v>32.86</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>21.71</v>
+        <v>21.84</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>14.92</v>
+        <v>15.05</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>10.05</v>
+        <v>10.18</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>8.06</v>
+        <v>8.17</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="80">
@@ -3175,31 +3175,31 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>92.36</v>
+        <v>92.33</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>76.45999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>27.5</v>
+        <v>27.57</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>18.54</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>14.41</v>
+        <v>14.44</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>9.789999999999999</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>6.11</v>
+        <v>6.18</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="81">
@@ -3209,31 +3209,31 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>88.64</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>65.86</v>
+        <v>65.89</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>41.53</v>
+        <v>41.6</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>36.79</v>
+        <v>36.9</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>34.71</v>
+        <v>34.85</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>31.32</v>
+        <v>31.45</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>23.62</v>
+        <v>23.72</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>21.34</v>
+        <v>21.4</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>20.16</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="82">
@@ -3243,31 +3243,31 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>69.93000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>40.49</v>
+        <v>40.56</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>24.03</v>
+        <v>24.26</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>22.01</v>
+        <v>22.21</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>20.46</v>
+        <v>20.56</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>18.25</v>
+        <v>18.35</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>10.32</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>8.27</v>
+        <v>8.23</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>7.22</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="83">
@@ -3277,31 +3277,31 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>67.67</v>
+        <v>67.63</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>32.03</v>
+        <v>32.07</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>14.99</v>
+        <v>15.14</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>14.14</v>
+        <v>14.25</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>13.13</v>
+        <v>13.24</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>10.45</v>
+        <v>10.57</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>8.85</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>8.59</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="84">
@@ -3311,31 +3311,31 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>61.09</v>
+        <v>61.29</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>36.12</v>
+        <v>36.39</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>22.14</v>
+        <v>22.28</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>20.7</v>
+        <v>20.83</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>19.15</v>
+        <v>19.29</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>16.97</v>
+        <v>17.1</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>12.47</v>
+        <v>12.6</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>11.53</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="85">
@@ -3345,13 +3345,13 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>54.17</v>
+        <v>54.13</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>18.23</v>
+        <v>18.3</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>6.98</v>
+        <v>7.01</v>
       </c>
       <c r="E85" s="3" t="n">
         <v>6.18</v>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>18.51</v>
+        <v>18.31</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>21.53</v>
+        <v>21.56</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>0.9</v>
@@ -3447,19 +3447,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>22.28</v>
+        <v>22.18</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>6.65</v>
+        <v>6.72</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>1.61</v>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>29.23</v>
+        <v>29.33</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>4.77</v>
+        <v>4.81</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>1.88</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1.08</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5.58</v>
+        <v>5.48</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>3.9</v>
@@ -3695,31 +3695,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>14.08</v>
+        <v>13.84</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>11.39</v>
+        <v>11.36</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.36</v>
+        <v>11.32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>11.26</v>
+        <v>11.22</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>9.34</v>
+        <v>9.31</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6.35</v>
+        <v>6.32</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>5.88</v>
+        <v>5.85</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="6">
@@ -3729,31 +3729,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>15</v>
+        <v>14.69</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.64</v>
+        <v>12.5</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>12.57</v>
+        <v>12.43</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>12.36</v>
+        <v>12.22</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>11.01</v>
+        <v>10.87</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>6.94</v>
+        <v>6.88</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6.84</v>
+        <v>6.77</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="7">
@@ -3763,31 +3763,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>11.49</v>
+        <v>11.46</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.99</v>
+        <v>10.95</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>10.82</v>
+        <v>10.79</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>10.11</v>
+        <v>10.08</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>9.34</v>
+        <v>9.24</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8.84</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="8">
@@ -3797,22 +3797,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14.69</v>
+        <v>14.76</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12.47</v>
+        <v>12.57</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.33</v>
+        <v>12.43</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>12.26</v>
+        <v>12.36</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>11.81</v>
+        <v>11.91</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>11.42</v>
+        <v>11.53</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>8.609999999999999</v>
@@ -3831,22 +3831,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5.28</v>
+        <v>5.07</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -3865,16 +3865,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6.59</v>
+        <v>6.62</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>1.61</v>
@@ -3899,31 +3899,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>13.47</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>12.9</v>
+        <v>12.97</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>12.86</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>12.79</v>
-      </c>
       <c r="F11" s="3" t="n">
-        <v>7.11</v>
+        <v>7.15</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>6.36</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>6.32</v>
-      </c>
       <c r="I11" s="3" t="n">
-        <v>6.11</v>
+        <v>6.14</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="12">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5.24</v>
+        <v>3.7</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>2.65</v>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>7.5</v>
+        <v>6.74</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>3.4</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5.68</v>
+        <v>5.01</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1.98</v>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.9</v>
@@ -4069,31 +4069,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.96</v>
+        <v>2.55</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G16" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I16" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="J16" s="3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17">
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>32.15</v>
+        <v>32.12</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>27.12</v>
+        <v>27.26</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>26.81</v>
+        <v>26.94</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>25.49</v>
+        <v>25.62</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>12.99</v>
+        <v>13.09</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11.7</v>
+        <v>11.81</v>
       </c>
       <c r="H18" s="3" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>10.28</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <v>10.24</v>
-      </c>
       <c r="J18" s="3" t="n">
-        <v>9.58</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -4171,31 +4171,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>22.65</v>
+        <v>22.24</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>19.05</v>
+        <v>18.95</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>18.21</v>
+        <v>18.11</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>17.67</v>
+        <v>17.64</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>10.72</v>
+        <v>10.75</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>8.57</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>8.529999999999999</v>
-      </c>
       <c r="J19" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="20">
@@ -4205,28 +4205,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>19.38</v>
+        <v>19.24</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>15.94</v>
+        <v>15.9</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>15.56</v>
+        <v>15.52</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>15.24</v>
+        <v>15.21</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>8.539999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>7.22</v>
+        <v>7.19</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>4.65</v>
@@ -4239,31 +4239,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>33.97</v>
+        <v>33.43</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>28.12</v>
+        <v>28.26</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>27.02</v>
+        <v>27.15</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>26.11</v>
+        <v>26.24</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>16.16</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>12.97</v>
+        <v>13</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10.72</v>
+        <v>10.75</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>10.55</v>
+        <v>10.58</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="22">
@@ -4273,22 +4273,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>32.69</v>
+        <v>32.49</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>27.18</v>
+        <v>27.32</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>25.03</v>
+        <v>25.17</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>22.08</v>
+        <v>22.21</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>11.63</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>8.029999999999999</v>
@@ -4307,19 +4307,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>33.97</v>
+        <v>34.23</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>29.72</v>
+        <v>30.02</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.05</v>
+        <v>28.35</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>27.08</v>
+        <v>27.42</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>14.77</v>
+        <v>14.73</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>11.31</v>
@@ -4341,31 +4341,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>21.1</v>
+        <v>21.07</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>18.78</v>
+        <v>18.82</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>17.88</v>
+        <v>17.91</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>16.47</v>
+        <v>16.5</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>9.51</v>
+        <v>9.58</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>17.6</v>
+        <v>17.26</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>12.5</v>
@@ -4387,10 +4387,10 @@
         <v>8.09</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4.55</v>
+        <v>4.51</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>2.22</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>15.36</v>
+        <v>15.29</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>12.67</v>
@@ -4492,7 +4492,7 @@
         <v>4.4</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>2.62</v>
@@ -4511,16 +4511,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>38.81</v>
+        <v>38.94</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>33</v>
+        <v>33.06</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>29.67</v>
+        <v>29.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>22.65</v>
+        <v>22.68</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>9.140000000000001</v>
@@ -4545,22 +4545,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>62.74</v>
+        <v>62.64</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>56.6</v>
+        <v>56.53</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>50.69</v>
+        <v>50.66</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>42.15</v>
+        <v>42.12</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>16.35</v>
+        <v>16.32</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>14.41</v>
+        <v>14.37</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>12.29</v>
@@ -4579,31 +4579,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>80.84999999999999</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>74.45999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>69.93000000000001</v>
+        <v>70.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>64.48</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>46.37</v>
+        <v>46.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>26.78</v>
+        <v>26.71</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.82</v>
+        <v>18.75</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>17.88</v>
+        <v>17.81</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>15.29</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="32">
@@ -4613,31 +4613,31 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>42.01</v>
+        <v>41.88</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>38.51</v>
+        <v>38.58</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>36.6</v>
+        <v>36.63</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>34.51</v>
+        <v>34.62</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>22.92</v>
+        <v>22.95</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>12.81</v>
+        <v>12.74</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>9.1</v>
+        <v>8.99</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="33">
@@ -4647,31 +4647,31 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>50.5</v>
+        <v>50.37</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>42.14</v>
+        <v>42</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>38.98</v>
+        <v>39.01</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>34.17</v>
+        <v>34.24</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>24.29</v>
+        <v>24.5</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>4.87</v>
+        <v>4.84</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>3.43</v>
+        <v>3.39</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -4687,22 +4687,22 @@
         <v>28.8</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>26.61</v>
+        <v>26.75</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>25.34</v>
+        <v>25.44</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>16.53</v>
+        <v>16.63</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>5.51</v>
+        <v>5.54</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>2.12</v>
@@ -4715,28 +4715,28 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>41.44</v>
+        <v>41.37</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>37.87</v>
+        <v>37.91</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>34.75</v>
+        <v>34.78</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>32.4</v>
+        <v>32.44</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>21.54</v>
+        <v>21.65</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>5.95</v>
+        <v>6.03</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4.87</v>
+        <v>4.95</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>3.2</v>
@@ -4749,31 +4749,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>36.59</v>
+        <v>36.49</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>26.58</v>
+        <v>26.61</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>23.62</v>
+        <v>23.72</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>18.82</v>
+        <v>18.92</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8.06</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="37">
@@ -4786,28 +4786,28 @@
         <v>25.03</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>23.09</v>
+        <v>23.12</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>22.01</v>
+        <v>22.05</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>20.97</v>
+        <v>21.01</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>17.78</v>
+        <v>17.85</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>8.06</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>6.63</v>
+        <v>6.7</v>
       </c>
       <c r="I37" s="3" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J37" s="3" t="n">
         <v>6.49</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>6.46</v>
       </c>
     </row>
     <row r="38">
@@ -4817,16 +4817,16 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>21.81</v>
+        <v>21.88</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>21.47</v>
+        <v>21.54</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>21.14</v>
+        <v>21.2</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>20.9</v>
+        <v>20.97</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>16.97</v>
@@ -4851,31 +4851,31 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>14.44</v>
+        <v>14.55</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>14.03</v>
+        <v>14.13</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>13.51</v>
+        <v>13.61</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.23</v>
+        <v>13.33</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>10.1</v>
+        <v>10.17</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="40">
@@ -4885,22 +4885,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>22.98</v>
+        <v>22.92</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>22.72</v>
+        <v>22.68</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>21.34</v>
+        <v>21.3</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>21.07</v>
+        <v>21.03</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>15.52</v>
+        <v>15.46</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10.65</v>
+        <v>10.58</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>5.44</v>
@@ -4919,22 +4919,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>34.31</v>
+        <v>34.48</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>32.83</v>
+        <v>33.03</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>31.12</v>
+        <v>31.28</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>29.4</v>
+        <v>29.64</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>22.88</v>
+        <v>23.08</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>13.58</v>
+        <v>13.68</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>8.94</v>
@@ -4953,31 +4953,31 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>45.03</v>
+        <v>45</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>43.47</v>
+        <v>43.54</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>40.59</v>
+        <v>40.66</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>38.06</v>
+        <v>38.16</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>28.92</v>
+        <v>28.99</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>23.12</v>
+        <v>23.19</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>15.94</v>
+        <v>15.97</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>13.51</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>6.77</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="43">
@@ -4987,28 +4987,28 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>52.86</v>
+        <v>52.96</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>50.94</v>
+        <v>51.04</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>48.69</v>
+        <v>48.79</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46.03</v>
+        <v>46.14</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>38.58</v>
+        <v>38.64</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>33.43</v>
+        <v>33.53</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>28.43</v>
+        <v>28.53</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>18.75</v>
+        <v>18.78</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>12.06</v>
@@ -5021,31 +5021,31 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>61.88</v>
+        <v>61.84</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>58.02</v>
+        <v>58.06</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>56.15</v>
+        <v>56.22</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>53.61</v>
+        <v>53.72</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>43.61</v>
+        <v>43.68</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>39.65</v>
+        <v>39.72</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>34.13</v>
+        <v>34.2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>18.33</v>
+        <v>18.26</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.21</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="45">
@@ -5055,31 +5055,31 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>82.53</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>79.06999999999999</v>
+        <v>78.83</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>75.47</v>
+        <v>75.27</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>72.01000000000001</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>63.78</v>
+        <v>63.81</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>55.31</v>
+        <v>55.54</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>38.98</v>
+        <v>39.15</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>20.43</v>
+        <v>20.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>9.74</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -5089,31 +5089,31 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>58.64</v>
+        <v>58.7</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>56.45</v>
+        <v>56.55</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>54.57</v>
+        <v>54.64</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>52.92</v>
+        <v>52.99</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>45.67</v>
+        <v>45.7</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>36.42</v>
+        <v>36.49</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>11.59</v>
+        <v>11.63</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.96</v>
+        <v>6.99</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.81</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="47">
@@ -5123,31 +5123,31 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>63.73</v>
+        <v>63.84</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>60.31</v>
+        <v>60.38</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>57.37</v>
+        <v>57.44</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>55.62</v>
+        <v>55.73</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>40.77</v>
+        <v>41.07</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>24.44</v>
+        <v>24.59</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>7.7</v>
+        <v>7.74</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>6.73</v>
+        <v>6.77</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="48">
@@ -5160,16 +5160,16 @@
         <v>57.22</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>53.36</v>
+        <v>53.46</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>48.86</v>
+        <v>49.03</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46.47</v>
+        <v>46.67</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>38.17</v>
+        <v>38.37</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>17.71</v>
@@ -5194,28 +5194,28 @@
         <v>42.05</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>39.62</v>
+        <v>39.72</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>36.74</v>
+        <v>36.84</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>34.17</v>
+        <v>34.31</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>29.13</v>
+        <v>29.2</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>13.33</v>
+        <v>13.37</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>8.51</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>8.02</v>
+        <v>8.06</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>7.92</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="50">
@@ -5228,19 +5228,19 @@
         <v>15.42</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>14.65</v>
+        <v>14.72</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.68</v>
+        <v>13.74</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>12.57</v>
+        <v>12.63</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>11.32</v>
+        <v>11.39</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>6.28</v>
+        <v>6.35</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>2.59</v>
@@ -5262,16 +5262,16 @@
         <v>29.69</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>27.85</v>
+        <v>27.88</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>25.83</v>
+        <v>25.9</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>24.41</v>
+        <v>24.44</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>22.19</v>
+        <v>22.22</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>15.03</v>
@@ -5293,22 +5293,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>35.69</v>
+        <v>35.38</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>27.59</v>
+        <v>27.69</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>24.87</v>
+        <v>24.93</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>21.07</v>
+        <v>21.14</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>14.62</v>
+        <v>14.65</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>5.88</v>
@@ -5327,22 +5327,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>39.92</v>
+        <v>39.89</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>35.82</v>
+        <v>35.95</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>33.47</v>
+        <v>33.6</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>31.55</v>
+        <v>31.69</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>29</v>
+        <v>29.13</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>20.46</v>
+        <v>20.5</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>9.880000000000001</v>
@@ -5361,22 +5361,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>69.83</v>
+        <v>70</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>64.06</v>
+        <v>64.17</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>62.64</v>
+        <v>62.78</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>60.8</v>
+        <v>60.94</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>45.73</v>
+        <v>45.62</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>16.53</v>
@@ -5385,7 +5385,7 @@
         <v>11.18</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>10.35</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="55">
@@ -5395,25 +5395,25 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>72.38</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>70.03</v>
+        <v>70.16</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>64.34999999999999</v>
+        <v>64.45</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>62.57</v>
+        <v>62.63</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>60.01</v>
+        <v>60.11</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>17.24</v>
+        <v>17.27</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>13.24</v>
@@ -5429,31 +5429,31 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>68.58</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>66.53</v>
+        <v>66.63</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62.6</v>
+        <v>62.74</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>60.62</v>
+        <v>60.8</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>56.28</v>
+        <v>56.39</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>33.26</v>
+        <v>33.33</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>14.93</v>
+        <v>14.97</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>13.09</v>
+        <v>13.12</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>11.42</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="57">
@@ -5463,31 +5463,31 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>67.73999999999999</v>
+        <v>67.88</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>66.3</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>64.38</v>
+        <v>64.55</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>61.73</v>
+        <v>61.96</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>56.96</v>
+        <v>57.19</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>37.9</v>
+        <v>38.04</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>19.89</v>
+        <v>20.03</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>17</v>
+        <v>17.14</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>14.31</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="58">
@@ -5497,31 +5497,31 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>64.55</v>
+        <v>64.72</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>63.04</v>
+        <v>63.21</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>57.76</v>
+        <v>57.93</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>49.73</v>
+        <v>49.93</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>45.13</v>
+        <v>45.3</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>29.84</v>
+        <v>29.91</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>16.63</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>14.21</v>
+        <v>14.25</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>12.77</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="59">
@@ -5531,31 +5531,31 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>72.88</v>
+        <v>72.84</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>71.98</v>
+        <v>72.02</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>66.84999999999999</v>
+        <v>66.95</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>63.15</v>
+        <v>63.29</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>59.27</v>
+        <v>59.45</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>31.07</v>
+        <v>31.18</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>14.04</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>9.59</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>8.84</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -5571,13 +5571,13 @@
         <v>46.94</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>42.2</v>
+        <v>42.17</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>38.61</v>
+        <v>38.64</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>31.92</v>
+        <v>31.99</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>12.63</v>
@@ -5602,16 +5602,16 @@
         <v>34.13</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>24.93</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>21.28</v>
+        <v>21.32</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>17.36</v>
+        <v>17.4</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>4.13</v>
@@ -5633,19 +5633,19 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>19.22</v>
+        <v>19.35</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>18.35</v>
+        <v>18.48</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>15.83</v>
+        <v>15.89</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>14.11</v>
+        <v>14.21</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>11.93</v>
+        <v>12.03</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>2.28</v>
@@ -5667,16 +5667,16 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>10.87</v>
+        <v>10.9</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>5.73</v>
+        <v>5.76</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>4.97</v>
@@ -5701,28 +5701,28 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>27.45</v>
+        <v>27.69</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>26.98</v>
+        <v>27.18</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>26.04</v>
+        <v>26.24</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>24.33</v>
+        <v>24.53</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>22.21</v>
+        <v>22.41</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>6.15</v>
+        <v>6.18</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>5.01</v>
@@ -5735,31 +5735,31 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>55.38</v>
+        <v>55.58</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>53.56</v>
+        <v>53.76</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>52.02</v>
+        <v>52.25</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>48.99</v>
+        <v>49.23</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>42.54</v>
+        <v>42.74</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>12.4</v>
+        <v>12.43</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>6.08</v>
+        <v>6.12</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>4.27</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="66">
@@ -5769,31 +5769,31 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>80.8</v>
+        <v>80.87</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>74.62</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>72.47</v>
+        <v>72.64</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>68.58</v>
+        <v>68.78</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>56.22</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>19.34</v>
+        <v>19.41</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>6.32</v>
+        <v>6.39</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>5.8</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="67">
@@ -5803,22 +5803,22 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>92.84</v>
+        <v>92.81</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.87</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>90.73</v>
+        <v>90.86</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>87.67</v>
+        <v>87.77</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>75.91</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>36.86</v>
+        <v>36.96</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>22.55</v>
@@ -5837,31 +5837,31 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>65</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>64.03</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>61.7</v>
+        <v>61.94</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>53.33</v>
+        <v>53.54</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>34.27</v>
+        <v>34.31</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>23.54</v>
+        <v>23.58</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>15.94</v>
+        <v>16.01</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>10.66</v>
+        <v>10.73</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>10.03</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="69">
@@ -5871,31 +5871,31 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>75.91</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>74.45999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>70.73</v>
+        <v>70.77</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>60.58</v>
+        <v>60.62</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>33.57</v>
+        <v>33.4</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>25.47</v>
+        <v>25.37</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>15.89</v>
+        <v>15.73</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>9.44</v>
+        <v>9.41</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="70">
@@ -5905,31 +5905,31 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70.53</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>70.16</v>
+        <v>70.09</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>64.84999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>57.02</v>
+        <v>57.16</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>31.92</v>
+        <v>32.09</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>23.69</v>
+        <v>23.82</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>19.49</v>
+        <v>19.59</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>14.92</v>
+        <v>15.02</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>13.51</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="71">
@@ -5939,19 +5939,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>71.84</v>
+        <v>71.95</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>70.8</v>
+        <v>70.91</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>67.89</v>
+        <v>67.97</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>53.94</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>28.35</v>
+        <v>28.39</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>21.73</v>
@@ -5963,7 +5963,7 @@
         <v>16.96</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>15.74</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="72">
@@ -5976,28 +5976,28 @@
         <v>56.72</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>51.85</v>
+        <v>52.02</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>47.95</v>
+        <v>48.08</v>
       </c>
       <c r="E72" s="3" t="n">
         <v>26.41</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>15.15</v>
+        <v>15.12</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>11.9</v>
+        <v>11.86</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>11.29</v>
+        <v>11.26</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>10.79</v>
+        <v>10.75</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>9.07</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -6010,28 +6010,28 @@
         <v>43.3</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>38.54</v>
+        <v>38.65</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>31.81</v>
+        <v>31.94</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>6.91</v>
+        <v>6.94</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="74">
@@ -6041,31 +6041,31 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>32.9</v>
+        <v>32.93</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>31.05</v>
+        <v>31.25</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>21.61</v>
+        <v>21.71</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>6.85</v>
+        <v>6.92</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>4.91</v>
+        <v>4.97</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="I74" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J74" s="3" t="n">
         <v>3.26</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>3.19</v>
       </c>
     </row>
     <row r="75">
@@ -6075,19 +6075,19 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>21.39</v>
+        <v>21.46</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>19.27</v>
+        <v>19.34</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>12.36</v>
+        <v>12.47</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>5.24</v>
+        <v>5.31</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>3.37</v>
@@ -6109,13 +6109,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>35.92</v>
+        <v>36.12</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>33.3</v>
+        <v>33.53</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>14.92</v>
+        <v>13.47</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>4.97</v>
@@ -6143,22 +6143,22 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>42.71</v>
+        <v>42.78</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>35.45</v>
+        <v>35.62</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>9.58</v>
+        <v>8.94</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>2.92</v>
@@ -6177,22 +6177,22 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>73.58</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>58.89</v>
+        <v>59.13</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>17.57</v>
+        <v>17.53</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>10.03</v>
+        <v>10.1</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>8.23</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>3.96</v>
@@ -6211,31 +6211,31 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>78.83</v>
+        <v>79.03</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>32.83</v>
+        <v>32.86</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>21.71</v>
+        <v>21.84</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>14.92</v>
+        <v>15.05</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>10.05</v>
+        <v>10.18</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>8.06</v>
+        <v>8.17</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="80">
@@ -6245,31 +6245,31 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>92.36</v>
+        <v>92.33</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>76.45999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>27.5</v>
+        <v>27.57</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>18.54</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>14.41</v>
+        <v>14.44</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>9.789999999999999</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>6.11</v>
+        <v>6.18</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="81">
@@ -6279,31 +6279,31 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>88.64</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>65.86</v>
+        <v>65.89</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>41.53</v>
+        <v>41.6</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>36.79</v>
+        <v>36.9</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>34.71</v>
+        <v>34.85</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>31.32</v>
+        <v>31.45</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>23.62</v>
+        <v>23.72</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>21.34</v>
+        <v>21.4</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>20.16</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="82">
@@ -6313,31 +6313,31 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>69.93000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>40.49</v>
+        <v>40.56</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>24.03</v>
+        <v>24.26</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>22.01</v>
+        <v>22.21</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>20.46</v>
+        <v>20.56</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>18.25</v>
+        <v>18.35</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>10.32</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>8.27</v>
+        <v>8.23</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>7.22</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="83">
@@ -6347,31 +6347,31 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>67.67</v>
+        <v>67.63</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>32.03</v>
+        <v>32.07</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>14.99</v>
+        <v>15.14</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>14.14</v>
+        <v>14.25</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>13.13</v>
+        <v>13.24</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>10.45</v>
+        <v>10.57</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>8.85</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>8.59</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="84">
@@ -6381,31 +6381,31 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>61.09</v>
+        <v>61.29</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>36.12</v>
+        <v>36.39</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>22.14</v>
+        <v>22.28</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>20.7</v>
+        <v>20.83</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>19.15</v>
+        <v>19.29</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>16.97</v>
+        <v>17.1</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>12.47</v>
+        <v>12.6</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>11.53</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="85">
@@ -6415,13 +6415,13 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>54.17</v>
+        <v>54.13</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>18.23</v>
+        <v>18.3</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>6.98</v>
+        <v>7.01</v>
       </c>
       <c r="E85" s="3" t="n">
         <v>6.18</v>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>18.51</v>
+        <v>18.31</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -6483,7 +6483,7 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>21.53</v>
+        <v>21.56</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>0.9</v>
@@ -6517,19 +6517,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>22.28</v>
+        <v>22.18</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>6.65</v>
+        <v>6.72</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>1.61</v>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>29.23</v>
+        <v>29.33</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>4.77</v>
+        <v>4.81</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>1.88</v>
@@ -6817,7 +6817,7 @@
         <v>2880</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>31</v>
@@ -6854,7 +6854,7 @@
         <v>2976</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>116</v>
@@ -6891,31 +6891,31 @@
         <v>2976</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
@@ -6928,31 +6928,31 @@
         <v>2880</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7">
@@ -6965,31 +6965,31 @@
         <v>2976</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
@@ -7002,22 +7002,22 @@
         <v>2880</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>248</v>
@@ -7039,22 +7039,22 @@
         <v>2976</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>24</v>
@@ -7076,16 +7076,16 @@
         <v>2976</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>48</v>
@@ -7113,31 +7113,31 @@
         <v>2784</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E11" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>358</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>356</v>
-      </c>
       <c r="G11" s="6" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H11" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="I11" s="6" t="n">
         <v>177</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <v>176</v>
-      </c>
       <c r="J11" s="6" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -7150,7 +7150,7 @@
         <v>2976</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>79</v>
@@ -7187,7 +7187,7 @@
         <v>2880</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>98</v>
@@ -7224,7 +7224,7 @@
         <v>2976</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>59</v>
@@ -7261,7 +7261,7 @@
         <v>2880</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>26</v>
@@ -7298,31 +7298,31 @@
         <v>2976</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H16" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="J16" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>15</v>
-      </c>
       <c r="K16" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -7372,31 +7372,31 @@
         <v>2880</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I18" s="6" t="n">
+        <v>297</v>
+      </c>
+      <c r="J18" s="6" t="n">
         <v>296</v>
       </c>
-      <c r="J18" s="6" t="n">
-        <v>295</v>
-      </c>
       <c r="K18" s="6" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19">
@@ -7409,31 +7409,31 @@
         <v>2976</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I19" s="6" t="n">
+        <v>256</v>
+      </c>
+      <c r="J19" s="6" t="n">
         <v>255</v>
       </c>
-      <c r="J19" s="6" t="n">
-        <v>254</v>
-      </c>
       <c r="K19" s="6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20">
@@ -7446,28 +7446,28 @@
         <v>2880</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>134</v>
@@ -7483,31 +7483,31 @@
         <v>2976</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>481</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22">
@@ -7520,22 +7520,22 @@
         <v>2976</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>346</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>239</v>
@@ -7557,19 +7557,19 @@
         <v>2688</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>304</v>
@@ -7594,31 +7594,31 @@
         <v>2976</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25">
@@ -7631,7 +7631,7 @@
         <v>2880</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>360</v>
@@ -7643,10 +7643,10 @@
         <v>233</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>64</v>
@@ -7668,7 +7668,7 @@
         <v>2976</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>259</v>
@@ -7742,7 +7742,7 @@
         <v>2976</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>377</v>
@@ -7757,7 +7757,7 @@
         <v>131</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>78</v>
@@ -7779,16 +7779,16 @@
         <v>2976</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>272</v>
@@ -7816,22 +7816,22 @@
         <v>2880</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1807</v>
+        <v>1804</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>354</v>
@@ -7853,31 +7853,31 @@
         <v>2976</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>2406</v>
+        <v>2411</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>2216</v>
+        <v>2220</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>2081</v>
+        <v>2085</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1919</v>
+        <v>1924</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="32">
@@ -7890,31 +7890,31 @@
         <v>2880</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="33">
@@ -7927,31 +7927,31 @@
         <v>2976</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
@@ -7970,22 +7970,22 @@
         <v>857</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>63</v>
@@ -8001,28 +8001,28 @@
         <v>2688</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>86</v>
@@ -8038,31 +8038,31 @@
         <v>2976</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="37">
@@ -8078,28 +8078,28 @@
         <v>721</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J37" s="6" t="n">
+        <v>188</v>
+      </c>
+      <c r="K37" s="6" t="n">
         <v>187</v>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>186</v>
       </c>
     </row>
     <row r="38">
@@ -8112,16 +8112,16 @@
         <v>2976</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>505</v>
@@ -8149,31 +8149,31 @@
         <v>2880</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40">
@@ -8186,22 +8186,22 @@
         <v>2976</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>162</v>
@@ -8223,22 +8223,22 @@
         <v>2976</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>266</v>
@@ -8260,31 +8260,31 @@
         <v>2880</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J42" s="6" t="n">
         <v>389</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43">
@@ -8297,28 +8297,28 @@
         <v>2976</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>359</v>
@@ -8334,31 +8334,31 @@
         <v>2880</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1544</v>
+        <v>1547</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="45">
@@ -8371,31 +8371,31 @@
         <v>2976</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>2456</v>
+        <v>2448</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>2353</v>
+        <v>2346</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>2246</v>
+        <v>2240</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>2143</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1646</v>
+        <v>1653</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46">
@@ -8408,31 +8408,31 @@
         <v>2976</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47">
@@ -8445,31 +8445,31 @@
         <v>2688</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>1713</v>
+        <v>1716</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48">
@@ -8485,16 +8485,16 @@
         <v>1703</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1454</v>
+        <v>1459</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>527</v>
@@ -8522,28 +8522,28 @@
         <v>1211</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50">
@@ -8559,19 +8559,19 @@
         <v>459</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>77</v>
@@ -8596,16 +8596,16 @@
         <v>855</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>433</v>
@@ -8630,22 +8630,22 @@
         <v>2976</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>1062</v>
+        <v>1053</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>175</v>
@@ -8667,22 +8667,22 @@
         <v>2976</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>294</v>
@@ -8704,22 +8704,22 @@
         <v>2880</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>1905</v>
+        <v>1910</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1845</v>
+        <v>1848</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>476</v>
@@ -8728,7 +8728,7 @@
         <v>322</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55">
@@ -8741,25 +8741,25 @@
         <v>2976</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>1786</v>
+        <v>1789</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J55" s="6" t="n">
         <v>394</v>
@@ -8778,31 +8778,31 @@
         <v>2880</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1803</v>
+        <v>1807</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="57">
@@ -8815,31 +8815,31 @@
         <v>2976</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>1973</v>
+        <v>1977</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>1916</v>
+        <v>1921</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1837</v>
+        <v>1844</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>1695</v>
+        <v>1702</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="58">
@@ -8852,31 +8852,31 @@
         <v>2976</v>
       </c>
       <c r="C58" s="6" t="n">
-        <v>1921</v>
+        <v>1926</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>1876</v>
+        <v>1881</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1719</v>
+        <v>1724</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="I58" s="6" t="n">
         <v>495</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="59">
@@ -8889,31 +8889,31 @@
         <v>2784</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>1861</v>
+        <v>1864</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1758</v>
+        <v>1762</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>1650</v>
+        <v>1655</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>391</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="60">
@@ -8932,13 +8932,13 @@
         <v>1397</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>376</v>
@@ -8966,16 +8966,16 @@
         <v>983</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E61" s="6" t="n">
         <v>718</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H61" s="6" t="n">
         <v>119</v>
@@ -9000,19 +9000,19 @@
         <v>2976</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>68</v>
@@ -9037,16 +9037,16 @@
         <v>2880</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G63" s="6" t="n">
         <v>143</v>
@@ -9074,28 +9074,28 @@
         <v>2976</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K64" s="6" t="n">
         <v>149</v>
@@ -9111,31 +9111,31 @@
         <v>2976</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>1648</v>
+        <v>1654</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>1594</v>
+        <v>1600</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>1548</v>
+        <v>1555</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1458</v>
+        <v>1465</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66">
@@ -9148,31 +9148,31 @@
         <v>2880</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>2149</v>
+        <v>2154</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>2087</v>
+        <v>2092</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1975</v>
+        <v>1981</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>1619</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67">
@@ -9185,22 +9185,22 @@
         <v>2976</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>2735</v>
+        <v>2734</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>2700</v>
+        <v>2704</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>2609</v>
+        <v>2612</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="I67" s="6" t="n">
         <v>671</v>
@@ -9222,31 +9222,31 @@
         <v>2880</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>1872</v>
+        <v>1878</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>1844</v>
+        <v>1850</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1777</v>
+        <v>1784</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1536</v>
+        <v>1542</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69">
@@ -9259,31 +9259,31 @@
         <v>2976</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>2216</v>
+        <v>2220</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="70">
@@ -9296,31 +9296,31 @@
         <v>2976</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="71">
@@ -9333,19 +9333,19 @@
         <v>2688</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1903</v>
+        <v>1906</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>1450</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H71" s="6" t="n">
         <v>584</v>
@@ -9357,7 +9357,7 @@
         <v>456</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="72">
@@ -9373,28 +9373,28 @@
         <v>1688</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1543</v>
+        <v>1548</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>786</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="73">
@@ -9410,28 +9410,28 @@
         <v>1247</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74">
@@ -9444,31 +9444,31 @@
         <v>2976</v>
       </c>
       <c r="C74" s="6" t="n">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J74" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="K74" s="6" t="n">
         <v>97</v>
-      </c>
-      <c r="K74" s="6" t="n">
-        <v>95</v>
       </c>
     </row>
     <row r="75">
@@ -9481,19 +9481,19 @@
         <v>2880</v>
       </c>
       <c r="C75" s="6" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H75" s="6" t="n">
         <v>97</v>
@@ -9518,13 +9518,13 @@
         <v>2976</v>
       </c>
       <c r="C76" s="6" t="n">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>444</v>
+        <v>401</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>148</v>
@@ -9555,22 +9555,22 @@
         <v>2976</v>
       </c>
       <c r="C77" s="6" t="n">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>87</v>
@@ -9592,22 +9592,22 @@
         <v>2880</v>
       </c>
       <c r="C78" s="6" t="n">
-        <v>2119</v>
+        <v>2127</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>1696</v>
+        <v>1703</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>237</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I78" s="6" t="n">
         <v>114</v>
@@ -9629,31 +9629,31 @@
         <v>2976</v>
       </c>
       <c r="C79" s="6" t="n">
-        <v>2346</v>
+        <v>2352</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>2101</v>
+        <v>2108</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="80">
@@ -9666,31 +9666,31 @@
         <v>2880</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>2202</v>
+        <v>2191</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>534</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H80" s="6" t="n">
         <v>282</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="81">
@@ -9703,31 +9703,31 @@
         <v>2976</v>
       </c>
       <c r="C81" s="6" t="n">
-        <v>2638</v>
+        <v>2634</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="82">
@@ -9740,31 +9740,31 @@
         <v>2976</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="G82" s="6" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="H82" s="6" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="I82" s="6" t="n">
         <v>307</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83">
@@ -9777,31 +9777,31 @@
         <v>2688</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84">
@@ -9814,31 +9814,31 @@
         <v>2976</v>
       </c>
       <c r="C84" s="6" t="n">
-        <v>1818</v>
+        <v>1824</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="H84" s="6" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85">
@@ -9851,13 +9851,13 @@
         <v>2880</v>
       </c>
       <c r="C85" s="6" t="n">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>178</v>
@@ -9888,10 +9888,10 @@
         <v>2976</v>
       </c>
       <c r="C86" s="6" t="n">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E86" s="6" t="n">
         <v>2</v>
@@ -9925,7 +9925,7 @@
         <v>2880</v>
       </c>
       <c r="C87" s="6" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D87" s="6" t="n">
         <v>26</v>
@@ -9962,19 +9962,19 @@
         <v>2976</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>48</v>
@@ -9999,10 +9999,10 @@
         <v>2976</v>
       </c>
       <c r="C89" s="6" t="n">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E89" s="6" t="n">
         <v>56</v>

--- a/outputs/SA_negative_prices.xlsx
+++ b/outputs/SA_negative_prices.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -74,7 +76,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6579,108 +6581,12 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B89">
+  <conditionalFormatting sqref="B2:J89">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C89">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D89">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E89">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F89">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G89">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H89">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I89">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J89">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="10"/>
+        <cfvo type="num" val="50"/>
         <color rgb="0063BE7B"/>
         <color rgb="00FFEB84"/>
         <color rgb="00F8696B"/>
